--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484325_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484325_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.4466</v>
+        <v>7.2543</v>
       </c>
       <c r="E2" t="n">
-        <v>5.1065</v>
+        <v>5.9959</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3402</v>
+        <v>1.2585</v>
       </c>
       <c r="G2" t="n">
         <v>0.3905</v>
@@ -610,13 +610,13 @@
         <v>1.9534</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4397</v>
+        <v>0.3679</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1499</v>
+        <v>-0.2606</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7102000000000001</v>
+        <v>0.6284999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>4.5424</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.3974</v>
+        <v>4.8939</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3483</v>
+        <v>3.0355</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0491</v>
+        <v>1.8584</v>
       </c>
       <c r="G3" t="n">
         <v>3.3007</v>
@@ -688,13 +688,13 @@
         <v>2.1488</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3721</v>
+        <v>0.1244</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.271</v>
+        <v>-0.5838</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8989</v>
+        <v>0.7082000000000001</v>
       </c>
       <c r="V3" t="n">
         <v>1.2735</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B. HIDALGO GARRIGUES</t>
+          <t>G. CATANY BIGAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6915</v>
+        <v>2.3946</v>
       </c>
       <c r="E4" t="n">
-        <v>2.926</v>
+        <v>1.0422</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2345</v>
+        <v>1.3524</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6633</v>
+        <v>1.364</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.3195</v>
+        <v>0.9594</v>
       </c>
       <c r="I4" t="n">
-        <v>1.9828</v>
+        <v>0.4047</v>
       </c>
       <c r="J4" t="n">
-        <v>2.5854</v>
+        <v>2.068</v>
       </c>
       <c r="K4" t="n">
-        <v>0.06270000000000001</v>
+        <v>0.7188</v>
       </c>
       <c r="L4" t="n">
-        <v>2.5227</v>
+        <v>1.3492</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.9221</v>
+        <v>-0.704</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.3822</v>
+        <v>0.2405</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.5399</v>
+        <v>-0.9445</v>
       </c>
       <c r="P4" t="n">
-        <v>0.586</v>
+        <v>1.5627</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7581</v>
+        <v>1.5627</v>
       </c>
       <c r="S4" t="n">
-        <v>1.165</v>
+        <v>0.132</v>
       </c>
       <c r="T4" t="n">
-        <v>1.2355</v>
+        <v>-0.3617</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.07049999999999999</v>
+        <v>0.4937</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2772</v>
+        <v>-0.6642</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2772</v>
+        <v>-0.6642</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. CATANY BIGAS</t>
+          <t>B. HIDALGO GARRIGUES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.618</v>
+        <v>2.072</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1839</v>
+        <v>2.1976</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4341</v>
+        <v>-0.1256</v>
       </c>
       <c r="G5" t="n">
-        <v>1.364</v>
+        <v>0.6633</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9594</v>
+        <v>-1.3195</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4047</v>
+        <v>1.9828</v>
       </c>
       <c r="J5" t="n">
-        <v>2.068</v>
+        <v>2.5854</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7188</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3492</v>
+        <v>2.5227</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.704</v>
+        <v>-1.9221</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2405</v>
+        <v>-1.3822</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.9445</v>
+        <v>-0.5399</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5627</v>
+        <v>0.586</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.1721</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5627</v>
+        <v>1.7581</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3554</v>
+        <v>0.5454</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.22</v>
+        <v>0.507</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5754</v>
+        <v>0.0384</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6642</v>
+        <v>0.2772</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.6642</v>
+        <v>0.2772</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1785</v>
+        <v>-0.0444</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9072</v>
+        <v>-1.1301</v>
       </c>
       <c r="F6" t="n">
         <v>1.0857</v>
@@ -922,10 +922,10 @@
         <v>1.3674</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3631</v>
+        <v>0.1402</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2037</v>
+        <v>-0.0192</v>
       </c>
       <c r="U6" t="n">
         <v>0.1594</v>
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4904</v>
+        <v>-0.6926</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5469000000000001</v>
+        <v>0.3446</v>
       </c>
       <c r="F7" t="n">
         <v>-1.0373</v>
@@ -1000,10 +1000,10 @@
         <v>0.1953</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6136</v>
+        <v>0.4113</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5531</v>
+        <v>0.3508</v>
       </c>
       <c r="U7" t="n">
         <v>0.0605</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6698</v>
+        <v>-1.0621</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7989000000000001</v>
+        <v>0.5154</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.4686</v>
+        <v>-1.5776</v>
       </c>
       <c r="G8" t="n">
         <v>-0.2242</v>
@@ -1078,13 +1078,13 @@
         <v>0.3907</v>
       </c>
       <c r="S8" t="n">
-        <v>0.695</v>
+        <v>0.3026</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5668</v>
+        <v>0.2834</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1281</v>
+        <v>0.0192</v>
       </c>
       <c r="V8" t="n">
         <v>-0.5545</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6451</v>
+        <v>-1.334</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5175</v>
+        <v>-0.3153</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1276</v>
+        <v>-1.0187</v>
       </c>
       <c r="G9" t="n">
         <v>-1.0851</v>
@@ -1156,13 +1156,13 @@
         <v>0.7814</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1227</v>
+        <v>0.1885</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0138</v>
+        <v>0.216</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1365</v>
+        <v>-0.0275</v>
       </c>
       <c r="V9" t="n">
         <v>-1.2186</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I. MARTINEZ MESEGUER</t>
+          <t>J. REDA COLL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.8869</v>
+        <v>-4.5156</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.9585</v>
+        <v>-4.2864</v>
       </c>
       <c r="F10" t="n">
-        <v>1.0716</v>
+        <v>-0.2292</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.8754</v>
+        <v>-0.7649</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3515</v>
+        <v>0.4477</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.5239</v>
+        <v>-1.2126</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.9016999999999999</v>
+        <v>0.2786</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3224</v>
+        <v>0.4119</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5794</v>
+        <v>-0.1332</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.9737</v>
+        <v>-1.0435</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0291</v>
+        <v>0.0359</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.9445</v>
+        <v>-1.0793</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.7115</v>
+        <v>-2.3441</v>
       </c>
       <c r="Q10" t="n">
-        <v>-5.0789</v>
+        <v>-4.1022</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3674</v>
+        <v>1.7581</v>
       </c>
       <c r="S10" t="n">
-        <v>1.2545</v>
+        <v>-0.2428</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0221</v>
+        <v>-0.4628</v>
       </c>
       <c r="U10" t="n">
-        <v>1.2324</v>
+        <v>0.22</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5545</v>
+        <v>-1.1638</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5545</v>
+        <v>-1.1638</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. REDA COLL</t>
+          <t>A. REBOLLO BONET</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.6385</v>
+        <v>-5.5227</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.9735</v>
+        <v>-5.1244</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.665</v>
+        <v>-0.3983</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.7649</v>
+        <v>-1.1542</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4477</v>
+        <v>0.5718</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.2126</v>
+        <v>-1.726</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2786</v>
+        <v>0.7579</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4119</v>
+        <v>1.9442</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.1332</v>
+        <v>-1.1863</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.0435</v>
+        <v>-1.9121</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0359</v>
+        <v>-1.3725</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.0793</v>
+        <v>-0.5397</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.3441</v>
+        <v>-5.6649</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.1022</v>
+        <v>-7.0323</v>
       </c>
       <c r="R11" t="n">
-        <v>1.7581</v>
+        <v>1.3674</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3657</v>
+        <v>0.6871</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1499</v>
+        <v>0.2635</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2158</v>
+        <v>0.4237</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.1638</v>
+        <v>0.6093</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.8865</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.1638</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. REBOLLO BONET</t>
+          <t>I. MARTINEZ MESEGUER</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.3067</v>
+        <v>-5.5382</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.6905</v>
+        <v>-6.2013</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6162</v>
+        <v>0.6631</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.1542</v>
+        <v>-1.8754</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5718</v>
+        <v>-0.3515</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.726</v>
+        <v>-1.5239</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7579</v>
+        <v>-0.9016999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>1.9442</v>
+        <v>-0.3224</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.1863</v>
+        <v>-0.5794</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.9121</v>
+        <v>-0.9737</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.3725</v>
+        <v>-0.0291</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.5397</v>
+        <v>-0.9445</v>
       </c>
       <c r="P12" t="n">
-        <v>-5.6649</v>
+        <v>-3.7115</v>
       </c>
       <c r="Q12" t="n">
-        <v>-7.0323</v>
+        <v>-5.0789</v>
       </c>
       <c r="R12" t="n">
         <v>1.3674</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0968</v>
+        <v>0.6031</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3026</v>
+        <v>-0.2207</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2058</v>
+        <v>0.8238</v>
       </c>
       <c r="V12" t="n">
-        <v>0.6093</v>
+        <v>-0.5545</v>
       </c>
       <c r="W12" t="n">
-        <v>0.8865</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.2772</v>
+        <v>-0.5545</v>
       </c>
     </row>
     <row r="13">
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.305399999999999</v>
+        <v>-2.094800000000003</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.1367</v>
+        <v>-3.926299999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>1.831500000000001</v>
+        <v>1.8314</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.4199999999999992</v>
+        <v>-0.419999999999999</v>
       </c>
       <c r="H13" t="n">
         <v>2.9485</v>
@@ -1447,7 +1447,7 @@
         <v>9.306600000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>2.704500000000001</v>
+        <v>2.7045</v>
       </c>
       <c r="M13" t="n">
         <v>-12.431</v>
@@ -1468,10 +1468,10 @@
         <v>14.6507</v>
       </c>
       <c r="S13" t="n">
-        <v>2.0496</v>
+        <v>3.2597</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.498399999999999</v>
+        <v>-0.2881000000000001</v>
       </c>
       <c r="U13" t="n">
         <v>3.5479</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.900700000000001</v>
+        <v>9.4945</v>
       </c>
       <c r="E14" t="n">
-        <v>6.4005</v>
+        <v>6.805</v>
       </c>
       <c r="F14" t="n">
-        <v>2.5002</v>
+        <v>2.6895</v>
       </c>
       <c r="G14" t="n">
         <v>5.4737</v>
@@ -1546,13 +1546,13 @@
         <v>3.7115</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.1357</v>
+        <v>-0.542</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1829</v>
+        <v>-0.7784</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0472</v>
+        <v>0.2365</v>
       </c>
       <c r="V14" t="n">
         <v>1.8279</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. MARTIN TRENADO</t>
+          <t>J. SOLE PIE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5138</v>
+        <v>1.7502</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.665</v>
+        <v>1.2708</v>
       </c>
       <c r="F15" t="n">
-        <v>3.1788</v>
+        <v>0.4794</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.1635</v>
+        <v>0.9287</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.4331</v>
+        <v>0.9429</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2696</v>
+        <v>-0.0142</v>
       </c>
       <c r="J15" t="n">
-        <v>1.6241</v>
+        <v>2.237</v>
       </c>
       <c r="K15" t="n">
-        <v>0.949</v>
+        <v>2.1156</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6751</v>
+        <v>0.1214</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.7876</v>
+        <v>-1.3083</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.3822</v>
+        <v>-1.1727</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4054</v>
+        <v>-0.1356</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.586</v>
+        <v>1.9534</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.9069</v>
+        <v>-0.9767</v>
       </c>
       <c r="R15" t="n">
-        <v>3.3208</v>
+        <v>2.9301</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4902</v>
+        <v>0.0867</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.1554</v>
+        <v>-0.2667</v>
       </c>
       <c r="U15" t="n">
-        <v>1.6456</v>
+        <v>0.3534</v>
       </c>
       <c r="V15" t="n">
-        <v>1.7731</v>
+        <v>-1.2186</v>
       </c>
       <c r="W15" t="n">
-        <v>1.7731</v>
+        <v>0.2772</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. ESTEVES-GARCIA COFFI</t>
+          <t>J. MARTIN TRENADO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0103</v>
+        <v>1.6289</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9903999999999999</v>
+        <v>-1.0583</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0199</v>
+        <v>2.6872</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2986</v>
+        <v>-0.1635</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3937</v>
+        <v>-0.4331</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0951</v>
+        <v>0.2696</v>
       </c>
       <c r="J16" t="n">
-        <v>1.3925</v>
+        <v>1.6241</v>
       </c>
       <c r="K16" t="n">
-        <v>1.352</v>
+        <v>0.949</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0405</v>
+        <v>0.6751</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.0939</v>
+        <v>-1.7876</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9583</v>
+        <v>-1.3822</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1356</v>
+        <v>-0.4054</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7814</v>
+        <v>-0.586</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9767</v>
+        <v>-3.9069</v>
       </c>
       <c r="R16" t="n">
-        <v>1.7581</v>
+        <v>3.3208</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9266</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3523</v>
+        <v>-0.5487</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5743</v>
+        <v>1.154</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.9962</v>
+        <v>1.7731</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2224</v>
+        <v>1.7731</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. SOLE PIE</t>
+          <t>P. CAMPAÑA SOLER</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9658</v>
+        <v>1.4207</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8663</v>
+        <v>-0.4255</v>
       </c>
       <c r="F17" t="n">
-        <v>0.09950000000000001</v>
+        <v>1.8462</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9287</v>
+        <v>0.1784</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9429</v>
+        <v>0.8667</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0142</v>
+        <v>-0.6883</v>
       </c>
       <c r="J17" t="n">
-        <v>2.237</v>
+        <v>1.5565</v>
       </c>
       <c r="K17" t="n">
-        <v>2.1156</v>
+        <v>2.1092</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1214</v>
+        <v>-0.5527</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.3083</v>
+        <v>-1.3781</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.1727</v>
+        <v>-1.2425</v>
       </c>
       <c r="O17" t="n">
         <v>-0.1356</v>
       </c>
       <c r="P17" t="n">
-        <v>1.9534</v>
+        <v>1.3674</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R17" t="n">
-        <v>2.9301</v>
+        <v>3.3208</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6977</v>
+        <v>-0.1251</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6712</v>
+        <v>-0.5831</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0265</v>
+        <v>0.458</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2772</v>
+        <v>0.5545</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.4959</v>
+        <v>-0.5545</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. SEGARRA BAQUES</t>
+          <t>S. ESTEVES-GARCIA COFFI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.624</v>
+        <v>0.4813</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5003</v>
+        <v>0.7882</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1243</v>
+        <v>-0.3069</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.3878</v>
+        <v>0.2986</v>
       </c>
       <c r="H18" t="n">
-        <v>-3.2623</v>
+        <v>0.3937</v>
       </c>
       <c r="I18" t="n">
-        <v>1.8745</v>
+        <v>-0.0951</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3249</v>
+        <v>1.3925</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.2244</v>
+        <v>1.352</v>
       </c>
       <c r="L18" t="n">
-        <v>2.5493</v>
+        <v>0.0405</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.7127</v>
+        <v>-1.0939</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.0379</v>
+        <v>-0.9583</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6749000000000001</v>
+        <v>-0.1356</v>
       </c>
       <c r="P18" t="n">
-        <v>1.3674</v>
+        <v>0.7814</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3441</v>
+        <v>1.7581</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6445</v>
+        <v>0.3976</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1515</v>
+        <v>0.1501</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4929</v>
+        <v>0.2475</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.9962</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.2224</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. CAMPAÑA SOLER</t>
+          <t>Q. BARDÉS BADIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4729</v>
+        <v>0.1175</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.83</v>
+        <v>0.0209</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3029</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1784</v>
+        <v>0.2812</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8667</v>
+        <v>-0.0289</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6883</v>
+        <v>0.3101</v>
       </c>
       <c r="J19" t="n">
-        <v>1.5565</v>
+        <v>0.0814</v>
       </c>
       <c r="K19" t="n">
-        <v>2.1092</v>
+        <v>0.0409</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5527</v>
+        <v>0.0405</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.3781</v>
+        <v>0.1998</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.2425</v>
+        <v>-0.0698</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1356</v>
+        <v>0.2696</v>
       </c>
       <c r="P19" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>3.3208</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0729</v>
+        <v>-0.1637</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9876</v>
+        <v>-0.0605</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0854</v>
+        <v>-0.1032</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X. ALMIRALL CANALS</t>
+          <t>M. SEGARRA BAQUES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3013</v>
+        <v>0.1055</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4359</v>
+        <v>-1.2081</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1346</v>
+        <v>1.3136</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1217</v>
+        <v>-1.3878</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3515</v>
+        <v>-3.2623</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2298</v>
+        <v>1.8745</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7363</v>
+        <v>0.3249</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6958</v>
+        <v>-2.2244</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0405</v>
+        <v>2.5493</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6146</v>
+        <v>-1.7127</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3443</v>
+        <v>-1.0379</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2702</v>
+        <v>-0.6749000000000001</v>
       </c>
       <c r="P20" t="n">
-        <v>0.7814</v>
+        <v>1.3674</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R20" t="n">
-        <v>1.7581</v>
+        <v>2.3441</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3396</v>
+        <v>0.126</v>
       </c>
       <c r="T20" t="n">
-        <v>0.399</v>
+        <v>-0.5563</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0595</v>
+        <v>0.6822</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.9414</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Q. BARDÉS BADIA</t>
+          <t>X. ALMIRALL CANALS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1992</v>
+        <v>-0.0293</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0209</v>
+        <v>0.1325</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1783</v>
+        <v>-0.1618</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2812</v>
+        <v>0.1217</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0289</v>
+        <v>0.3515</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3101</v>
+        <v>-0.2298</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0814</v>
+        <v>0.7363</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0409</v>
+        <v>0.6958</v>
       </c>
       <c r="L21" t="n">
         <v>0.0405</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1998</v>
+        <v>-0.6146</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0698</v>
+        <v>-0.3443</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2696</v>
+        <v>-0.2702</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>0.7814</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.7581</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.082</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0605</v>
+        <v>0.09569999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0215</v>
+        <v>-0.0867</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.9414</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.9205</v>
+        <v>-1.0022</v>
       </c>
       <c r="E22" t="n">
         <v>-0.6123</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3082</v>
+        <v>-0.3899</v>
       </c>
       <c r="G22" t="n">
         <v>-0.6218</v>
@@ -2170,13 +2170,13 @@
         <v>0.1953</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2168</v>
+        <v>-0.2985</v>
       </c>
       <c r="T22" t="n">
         <v>-0.0605</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1563</v>
+        <v>-0.238</v>
       </c>
       <c r="V22" t="n">
         <v>-0.2772</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.8444</v>
+        <v>-1.8171</v>
       </c>
       <c r="E23" t="n">
         <v>-1.5694</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.275</v>
+        <v>-0.2477</v>
       </c>
       <c r="G23" t="n">
         <v>-1.8763</v>
@@ -2248,13 +2248,13 @@
         <v>0.3907</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3588</v>
+        <v>-0.3315</v>
       </c>
       <c r="T23" t="n">
         <v>-0.3026</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0561</v>
+        <v>-0.0289</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.6653</v>
+        <v>-2.778</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.6912</v>
+        <v>-1.9946</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.974</v>
+        <v>-0.7834</v>
       </c>
       <c r="G24" t="n">
         <v>-0.8985</v>
@@ -2326,13 +2326,13 @@
         <v>1.5627</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5249</v>
+        <v>-0.6375999999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1732</v>
+        <v>-0.4766</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3517</v>
+        <v>-0.161</v>
       </c>
       <c r="V24" t="n">
         <v>-1.8279</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.2526</v>
+        <v>-5.3925</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.6773</v>
+        <v>-3.9806</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.5753</v>
+        <v>-1.4119</v>
       </c>
       <c r="G25" t="n">
         <v>-1.9144</v>
@@ -2404,13 +2404,13 @@
         <v>1.1721</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.3615</v>
+        <v>-0.5014</v>
       </c>
       <c r="T25" t="n">
-        <v>0.1432</v>
+        <v>-0.1602</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.5046</v>
+        <v>-0.3412</v>
       </c>
       <c r="V25" t="n">
         <v>-1.2186</v>
@@ -2437,19 +2437,19 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>3.3052</v>
+        <v>3.9795</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.8315</v>
+        <v>-1.831400000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>5.136799999999999</v>
+        <v>5.810899999999999</v>
       </c>
       <c r="G26" t="n">
         <v>0.4199999999999995</v>
       </c>
       <c r="H26" t="n">
-        <v>-2.9485</v>
+        <v>-2.948500000000001</v>
       </c>
       <c r="I26" t="n">
         <v>3.368600000000001</v>
@@ -2470,7 +2470,7 @@
         <v>-9.306700000000001</v>
       </c>
       <c r="O26" t="n">
-        <v>-2.704199999999999</v>
+        <v>-2.7042</v>
       </c>
       <c r="P26" t="n">
         <v>7.8137</v>
@@ -2482,13 +2482,13 @@
         <v>22.4643</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.0494</v>
+        <v>-1.3752</v>
       </c>
       <c r="T26" t="n">
-        <v>-3.547900000000001</v>
+        <v>-3.5478</v>
       </c>
       <c r="U26" t="n">
-        <v>1.4984</v>
+        <v>2.1726</v>
       </c>
       <c r="V26" t="n">
         <v>-2.8789</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484325_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484325_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0.0549</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484325_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.5545</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484325_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484325_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484325_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0.3321</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484325_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484325_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.5545</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484325_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484325_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.1638</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484325_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484325_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-0.5545</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484325_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-3.9361</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0.6642</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484325_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.4959</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484325_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,11 +1790,16 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484325_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. CAMPAÑA SOLER</t>
+          <t>P. CAMPANA SOLER</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,28 +1811,28 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.4207</v>
+        <v>0.8067</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.4255</v>
+        <v>-1.0395</v>
       </c>
       <c r="F17" t="n">
         <v>1.8462</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1784</v>
+        <v>-0.4356</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8667</v>
+        <v>0.2528</v>
       </c>
       <c r="I17" t="n">
         <v>-0.6883</v>
       </c>
       <c r="J17" t="n">
-        <v>1.5565</v>
+        <v>0.9426</v>
       </c>
       <c r="K17" t="n">
-        <v>2.1092</v>
+        <v>1.4953</v>
       </c>
       <c r="L17" t="n">
         <v>-0.5527</v>
@@ -1796,12 +1872,17 @@
       </c>
       <c r="X17" t="n">
         <v>-0.5545</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484325_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. ESTEVES-GARCIA COFFI</t>
+          <t>P. CAMPAÑA SOLER</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4813</v>
+        <v>0.614</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7882</v>
+        <v>0.614</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3069</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2986</v>
+        <v>0.614</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3937</v>
+        <v>0.614</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0951</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1.3925</v>
+        <v>0.614</v>
       </c>
       <c r="K18" t="n">
-        <v>1.352</v>
+        <v>0.614</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0405</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.0939</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9583</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1356</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7581</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3976</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1501</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2475</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.9962</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2224</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484325_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Q. BARDÉS BADIA</t>
+          <t>S. ESTEVES-GARCIA COFFI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1175</v>
+        <v>0.4813</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0209</v>
+        <v>0.7882</v>
       </c>
       <c r="F19" t="n">
-        <v>0.09660000000000001</v>
+        <v>-0.3069</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2812</v>
+        <v>0.2986</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0289</v>
+        <v>0.3937</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3101</v>
+        <v>-0.0951</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0814</v>
+        <v>1.3925</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0409</v>
+        <v>1.352</v>
       </c>
       <c r="L19" t="n">
         <v>0.0405</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1998</v>
+        <v>-1.0939</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0698</v>
+        <v>-0.9583</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2696</v>
+        <v>-0.1356</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.7814</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.7581</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1637</v>
+        <v>0.3976</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0605</v>
+        <v>0.1501</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1032</v>
+        <v>0.2475</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.9962</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.2224</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484325_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. SEGARRA BAQUES</t>
+          <t>Q. BARDES BADIA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +2060,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1055</v>
+        <v>0.1175</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2081</v>
+        <v>0.0209</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3136</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.3878</v>
+        <v>0.2812</v>
       </c>
       <c r="H20" t="n">
-        <v>-3.2623</v>
+        <v>-0.0289</v>
       </c>
       <c r="I20" t="n">
-        <v>1.8745</v>
+        <v>0.3101</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3249</v>
+        <v>0.0814</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.2244</v>
+        <v>0.0409</v>
       </c>
       <c r="L20" t="n">
-        <v>2.5493</v>
+        <v>0.0405</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.7127</v>
+        <v>0.1998</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.0379</v>
+        <v>-0.0698</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6749000000000001</v>
+        <v>0.2696</v>
       </c>
       <c r="P20" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.3441</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.126</v>
+        <v>-0.1637</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5563</v>
+        <v>-0.0605</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6822</v>
+        <v>-0.1032</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2030,12 +2121,17 @@
       </c>
       <c r="X20" t="n">
         <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484325_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X. ALMIRALL CANALS</t>
+          <t>M. SEGARRA BAQUES</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0293</v>
+        <v>0.1055</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1325</v>
+        <v>-1.2081</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1618</v>
+        <v>1.3136</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1217</v>
+        <v>-1.3878</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3515</v>
+        <v>-3.2623</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2298</v>
+        <v>1.8745</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7363</v>
+        <v>0.3249</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6958</v>
+        <v>-2.2244</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0405</v>
+        <v>2.5493</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.6146</v>
+        <v>-1.7127</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3443</v>
+        <v>-1.0379</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2702</v>
+        <v>-0.6749000000000001</v>
       </c>
       <c r="P21" t="n">
-        <v>0.7814</v>
+        <v>1.3674</v>
       </c>
       <c r="Q21" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R21" t="n">
-        <v>1.7581</v>
+        <v>2.3441</v>
       </c>
       <c r="S21" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.126</v>
       </c>
       <c r="T21" t="n">
-        <v>0.09569999999999999</v>
+        <v>-0.5563</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0867</v>
+        <v>0.6822</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.9414</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484325_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. SELLARÈS GIRALT</t>
+          <t>X. ALMIRALL CANALS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.0022</v>
+        <v>-0.0293</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.6123</v>
+        <v>0.1325</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3899</v>
+        <v>-0.1618</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.6218</v>
+        <v>0.1217</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.6621</v>
+        <v>0.3515</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0403</v>
+        <v>-0.2298</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.5518</v>
+        <v>0.7363</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.5921999999999999</v>
+        <v>0.6958</v>
       </c>
       <c r="L22" t="n">
         <v>0.0405</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.6146</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.0698</v>
+        <v>-0.3443</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.0002</v>
+        <v>-0.2702</v>
       </c>
       <c r="P22" t="n">
-        <v>0.1953</v>
+        <v>0.7814</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R22" t="n">
-        <v>0.1953</v>
+        <v>1.7581</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2985</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0605</v>
+        <v>0.09569999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.238</v>
+        <v>-0.0867</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.2772</v>
+        <v>-0.9414</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2772</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484325_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S. ROMEO FO</t>
+          <t>M. SELLARES GIRALT</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.8171</v>
+        <v>-1.0022</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.5694</v>
+        <v>-0.6123</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2477</v>
+        <v>-0.3899</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.8763</v>
+        <v>-0.6218</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.5119</v>
+        <v>-0.6621</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.3644</v>
+        <v>0.0403</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.2668</v>
+        <v>-0.5518</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.3073</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="L23" t="n">
         <v>0.0405</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.6095</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.2047</v>
+        <v>-0.0698</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4049</v>
+        <v>-0.0002</v>
       </c>
       <c r="P23" t="n">
-        <v>0.3907</v>
+        <v>0.1953</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.3907</v>
+        <v>0.1953</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3315</v>
+        <v>-0.2985</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3026</v>
+        <v>-0.0605</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0289</v>
+        <v>-0.238</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484325_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. ROSADO FORNIES</t>
+          <t>S. ROMEO FO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2392,78 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.778</v>
+        <v>-1.8171</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.9946</v>
+        <v>-1.5694</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.7834</v>
+        <v>-0.2477</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.8985</v>
+        <v>-1.8763</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.6263</v>
+        <v>-1.5119</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7278</v>
+        <v>-0.3644</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.2092</v>
+        <v>-1.2668</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.9376</v>
+        <v>-1.3073</v>
       </c>
       <c r="L24" t="n">
-        <v>0.7284</v>
+        <v>0.0405</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.6893</v>
+        <v>-0.6095</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.6887</v>
+        <v>-0.2047</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.4049</v>
       </c>
       <c r="P24" t="n">
-        <v>0.586</v>
+        <v>0.3907</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5627</v>
+        <v>0.3907</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6375999999999999</v>
+        <v>-0.3315</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4766</v>
+        <v>-0.3026</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.161</v>
+        <v>-0.0289</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.8279</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484325_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>D. ROY CARNICER</t>
+          <t>M. ROSADO FORNIES</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2475,78 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.3925</v>
+        <v>-2.778</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.9806</v>
+        <v>-1.9946</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.4119</v>
+        <v>-0.7834</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.9144</v>
+        <v>-0.8985</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.4963</v>
+        <v>-1.6263</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.4181</v>
+        <v>0.7278</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.8903</v>
+        <v>-0.2092</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.8774999999999999</v>
+        <v>-0.9376</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.0128</v>
+        <v>0.7284</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.0241</v>
+        <v>-0.6893</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.6188</v>
+        <v>-0.6887</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.4052</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.7581</v>
+        <v>0.586</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R25" t="n">
-        <v>1.1721</v>
+        <v>1.5627</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.5014</v>
+        <v>-0.6375999999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1602</v>
+        <v>-0.4766</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3412</v>
+        <v>-0.161</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.2186</v>
+        <v>-1.8279</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>-0.3321</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.2186</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484325_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>D. ROY CARNICER</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,68 +2558,152 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
+        <v>-5.3925</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-3.9806</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-1.4119</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-1.9144</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-1.4963</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-0.4181</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-0.8903</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-0.8774999999999999</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-0.0128</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-1.0241</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-0.6188</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-0.4052</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-1.7581</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-2.9301</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.1721</v>
+      </c>
+      <c r="S26" t="n">
+        <v>-0.5014</v>
+      </c>
+      <c r="T26" t="n">
+        <v>-0.1602</v>
+      </c>
+      <c r="U26" t="n">
+        <v>-0.3412</v>
+      </c>
+      <c r="V26" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484325_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>TENEA-C.B. ESPARREGUERA</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
         <v>3.9795</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E27" t="n">
         <v>-1.831400000000001</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F27" t="n">
         <v>5.810899999999999</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G27" t="n">
         <v>0.4199999999999995</v>
       </c>
-      <c r="H26" t="n">
-        <v>-2.948500000000001</v>
-      </c>
-      <c r="I26" t="n">
+      <c r="H27" t="n">
+        <v>-2.9484</v>
+      </c>
+      <c r="I27" t="n">
         <v>3.368600000000001</v>
       </c>
-      <c r="J26" t="n">
-        <v>12.431</v>
-      </c>
-      <c r="K26" t="n">
-        <v>6.3581</v>
-      </c>
-      <c r="L26" t="n">
+      <c r="J27" t="n">
+        <v>12.4311</v>
+      </c>
+      <c r="K27" t="n">
+        <v>6.358200000000002</v>
+      </c>
+      <c r="L27" t="n">
         <v>6.073</v>
       </c>
-      <c r="M26" t="n">
+      <c r="M27" t="n">
         <v>-12.0109</v>
       </c>
-      <c r="N26" t="n">
-        <v>-9.306700000000001</v>
-      </c>
-      <c r="O26" t="n">
+      <c r="N27" t="n">
+        <v>-9.306699999999999</v>
+      </c>
+      <c r="O27" t="n">
         <v>-2.7042</v>
       </c>
-      <c r="P26" t="n">
+      <c r="P27" t="n">
         <v>7.8137</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="Q27" t="n">
         <v>-14.6506</v>
       </c>
-      <c r="R26" t="n">
+      <c r="R27" t="n">
         <v>22.4643</v>
       </c>
-      <c r="S26" t="n">
+      <c r="S27" t="n">
         <v>-1.3752</v>
       </c>
-      <c r="T26" t="n">
+      <c r="T27" t="n">
         <v>-3.5478</v>
       </c>
-      <c r="U26" t="n">
-        <v>2.1726</v>
-      </c>
-      <c r="V26" t="n">
+      <c r="U27" t="n">
+        <v>2.172599999999999</v>
+      </c>
+      <c r="V27" t="n">
         <v>-2.8789</v>
       </c>
-      <c r="W26" t="n">
+      <c r="W27" t="n">
         <v>3.936099999999999</v>
       </c>
-      <c r="X26" t="n">
+      <c r="X27" t="n">
         <v>-6.815099999999999</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
